--- a/backend/data/financials_by_company/1598.HK.xlsx
+++ b/backend/data/financials_by_company/1598.HK.xlsx
@@ -652,142 +652,142 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>253000</v>
+        <v>2990000</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>166417000</v>
+        <v>90024000</v>
       </c>
       <c r="E2" t="n">
-        <v>1012000</v>
+        <v>11960000</v>
       </c>
       <c r="F2" t="n">
-        <v>1012000</v>
+        <v>11960000</v>
       </c>
       <c r="G2" t="n">
-        <v>39911000</v>
+        <v>29180000</v>
       </c>
       <c r="H2" t="n">
-        <v>85882000</v>
+        <v>47526000</v>
       </c>
       <c r="I2" t="n">
-        <v>255069000</v>
+        <v>181942000</v>
       </c>
       <c r="J2" t="n">
-        <v>167429000</v>
+        <v>101984000</v>
       </c>
       <c r="K2" t="n">
-        <v>81547000</v>
+        <v>54458000</v>
       </c>
       <c r="L2" t="n">
-        <v>-31620000</v>
+        <v>-14078000</v>
       </c>
       <c r="M2" t="n">
-        <v>42387000</v>
+        <v>26064000</v>
       </c>
       <c r="N2" t="n">
-        <v>11125000</v>
+        <v>12555000</v>
       </c>
       <c r="O2" t="n">
-        <v>39152000</v>
+        <v>20210000</v>
       </c>
       <c r="P2" t="n">
-        <v>39911000</v>
+        <v>29180000</v>
       </c>
       <c r="Q2" t="n">
-        <v>348439000</v>
+        <v>263014000</v>
       </c>
       <c r="R2" t="n">
-        <v>1141816716</v>
+        <v>1140307446</v>
       </c>
       <c r="S2" t="n">
-        <v>1141262609</v>
+        <v>1139256694</v>
       </c>
       <c r="T2" t="n">
-        <v>0.035</v>
+        <v>0.0256</v>
       </c>
       <c r="U2" t="n">
-        <v>0.035</v>
+        <v>0.0256</v>
       </c>
       <c r="V2" t="n">
-        <v>39911000</v>
+        <v>29180000</v>
       </c>
       <c r="W2" t="n">
-        <v>39911000</v>
+        <v>29180000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>39911000</v>
+        <v>29180000</v>
       </c>
       <c r="Z2" t="n">
-        <v>75000</v>
+        <v>440000</v>
       </c>
       <c r="AA2" t="n">
-        <v>39836000</v>
+        <v>28740000</v>
       </c>
       <c r="AB2" t="n">
-        <v>39836000</v>
+        <v>28740000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-676000</v>
+        <v>-346000</v>
       </c>
       <c r="AD2" t="n">
-        <v>39160000</v>
+        <v>28394000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4763000</v>
+        <v>-29080000</v>
       </c>
       <c r="AF2" t="n">
-        <v>92000</v>
+        <v>550000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-92000</v>
+        <v>-550000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-31620000</v>
+        <v>-14078000</v>
       </c>
       <c r="AI2" t="n">
-        <v>358000</v>
+        <v>569000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>42387000</v>
+        <v>26064000</v>
       </c>
       <c r="AK2" t="n">
-        <v>11125000</v>
+        <v>12555000</v>
       </c>
       <c r="AL2" t="n">
-        <v>71589000</v>
+        <v>45753000</v>
       </c>
       <c r="AM2" t="n">
-        <v>93370000</v>
+        <v>81072000</v>
       </c>
       <c r="AN2" t="n">
-        <v>108926000</v>
+        <v>89097000</v>
       </c>
       <c r="AO2" t="n">
-        <v>26227000</v>
+        <v>17921000</v>
       </c>
       <c r="AP2" t="n">
-        <v>82699000</v>
+        <v>71176000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>164959000</v>
+        <v>126825000</v>
       </c>
       <c r="AR2" t="n">
-        <v>255069000</v>
+        <v>181942000</v>
       </c>
       <c r="AS2" t="n">
-        <v>420028000</v>
+        <v>308767000</v>
       </c>
       <c r="AT2" t="n">
-        <v>420028000</v>
+        <v>308767000</v>
       </c>
     </row>
     <row r="3">
@@ -932,142 +932,142 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>2990000</v>
+        <v>253000</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>90024000</v>
+        <v>166417000</v>
       </c>
       <c r="E4" t="n">
-        <v>11960000</v>
+        <v>1012000</v>
       </c>
       <c r="F4" t="n">
-        <v>11960000</v>
+        <v>1012000</v>
       </c>
       <c r="G4" t="n">
-        <v>29180000</v>
+        <v>39911000</v>
       </c>
       <c r="H4" t="n">
-        <v>47526000</v>
+        <v>85882000</v>
       </c>
       <c r="I4" t="n">
-        <v>181942000</v>
+        <v>255069000</v>
       </c>
       <c r="J4" t="n">
-        <v>101984000</v>
+        <v>167429000</v>
       </c>
       <c r="K4" t="n">
-        <v>54458000</v>
+        <v>81547000</v>
       </c>
       <c r="L4" t="n">
-        <v>-14078000</v>
+        <v>-31620000</v>
       </c>
       <c r="M4" t="n">
-        <v>26064000</v>
+        <v>42387000</v>
       </c>
       <c r="N4" t="n">
-        <v>12555000</v>
+        <v>11125000</v>
       </c>
       <c r="O4" t="n">
-        <v>20210000</v>
+        <v>39152000</v>
       </c>
       <c r="P4" t="n">
-        <v>29180000</v>
+        <v>39911000</v>
       </c>
       <c r="Q4" t="n">
-        <v>263014000</v>
+        <v>348439000</v>
       </c>
       <c r="R4" t="n">
-        <v>1140307446</v>
+        <v>1141816716</v>
       </c>
       <c r="S4" t="n">
-        <v>1139256694</v>
+        <v>1141262609</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0256</v>
+        <v>0.035</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0256</v>
+        <v>0.035</v>
       </c>
       <c r="V4" t="n">
-        <v>29180000</v>
+        <v>39911000</v>
       </c>
       <c r="W4" t="n">
-        <v>29180000</v>
+        <v>39911000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>29180000</v>
+        <v>39911000</v>
       </c>
       <c r="Z4" t="n">
-        <v>440000</v>
+        <v>75000</v>
       </c>
       <c r="AA4" t="n">
-        <v>28740000</v>
+        <v>39836000</v>
       </c>
       <c r="AB4" t="n">
-        <v>28740000</v>
+        <v>39836000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-346000</v>
+        <v>-676000</v>
       </c>
       <c r="AD4" t="n">
-        <v>28394000</v>
+        <v>39160000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-29080000</v>
+        <v>-4763000</v>
       </c>
       <c r="AF4" t="n">
-        <v>550000</v>
+        <v>92000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-550000</v>
+        <v>-92000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-14078000</v>
+        <v>-31620000</v>
       </c>
       <c r="AI4" t="n">
-        <v>569000</v>
+        <v>358000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26064000</v>
+        <v>42387000</v>
       </c>
       <c r="AK4" t="n">
-        <v>12555000</v>
+        <v>11125000</v>
       </c>
       <c r="AL4" t="n">
-        <v>45753000</v>
+        <v>71589000</v>
       </c>
       <c r="AM4" t="n">
-        <v>81072000</v>
+        <v>93370000</v>
       </c>
       <c r="AN4" t="n">
-        <v>89097000</v>
+        <v>108926000</v>
       </c>
       <c r="AO4" t="n">
-        <v>17921000</v>
+        <v>26227000</v>
       </c>
       <c r="AP4" t="n">
-        <v>71176000</v>
+        <v>82699000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>126825000</v>
+        <v>164959000</v>
       </c>
       <c r="AR4" t="n">
-        <v>181942000</v>
+        <v>255069000</v>
       </c>
       <c r="AS4" t="n">
-        <v>308767000</v>
+        <v>420028000</v>
       </c>
       <c r="AT4" t="n">
-        <v>308767000</v>
+        <v>420028000</v>
       </c>
     </row>
   </sheetData>
@@ -1433,208 +1433,212 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1161204000</v>
+        <v>1167216000</v>
       </c>
       <c r="C2" t="n">
-        <v>1161204000</v>
+        <v>1167216000</v>
       </c>
       <c r="D2" t="n">
-        <v>605407000</v>
+        <v>112136000</v>
       </c>
       <c r="E2" t="n">
-        <v>951860000</v>
+        <v>483417000</v>
       </c>
       <c r="F2" t="n">
-        <v>198025000</v>
+        <v>514782000</v>
       </c>
       <c r="G2" t="n">
-        <v>1654021000</v>
+        <v>1124310000</v>
       </c>
       <c r="H2" t="n">
-        <v>-315233000</v>
+        <v>146172000</v>
       </c>
       <c r="I2" t="n">
-        <v>198025000</v>
+        <v>514782000</v>
       </c>
       <c r="J2" t="n">
-        <v>76199000</v>
+        <v>36949000</v>
       </c>
       <c r="K2" t="n">
-        <v>778360000</v>
+        <v>677842000</v>
       </c>
       <c r="L2" t="n">
-        <v>1082921000</v>
+        <v>788508000</v>
       </c>
       <c r="M2" t="n">
-        <v>781185000</v>
+        <v>685787000</v>
       </c>
       <c r="N2" t="n">
-        <v>2825000</v>
+        <v>7945000</v>
       </c>
       <c r="O2" t="n">
-        <v>778360000</v>
+        <v>677842000</v>
       </c>
       <c r="P2" t="n">
-        <v>2623000</v>
+        <v>5844000</v>
       </c>
       <c r="Q2" t="n">
-        <v>168000</v>
+        <v>176000</v>
       </c>
       <c r="R2" t="n">
-        <v>241942000</v>
+        <v>217067000</v>
       </c>
       <c r="S2" t="n">
-        <v>228298000</v>
+        <v>237765000</v>
       </c>
       <c r="T2" t="n">
-        <v>9750000</v>
+        <v>9801000</v>
       </c>
       <c r="U2" t="n">
-        <v>9750000</v>
+        <v>9801000</v>
       </c>
       <c r="V2" t="n">
-        <v>1541564000</v>
+        <v>688296000</v>
       </c>
       <c r="W2" t="n">
-        <v>552008000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>7894000</v>
-      </c>
+        <v>135042000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2978000</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>165097000</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>5924000</v>
+        <v>741000</v>
       </c>
       <c r="AB2" t="n">
-        <v>373093000</v>
+        <v>131323000</v>
       </c>
       <c r="AC2" t="n">
-        <v>68532000</v>
+        <v>20657000</v>
       </c>
       <c r="AD2" t="n">
-        <v>304561000</v>
+        <v>110666000</v>
       </c>
       <c r="AE2" t="n">
-        <v>989556000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>553254000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>863000</v>
+      </c>
       <c r="AG2" t="n">
-        <v>578767000</v>
+        <v>352094000</v>
       </c>
       <c r="AH2" t="n">
-        <v>7667000</v>
+        <v>16292000</v>
       </c>
       <c r="AI2" t="n">
-        <v>571100000</v>
+        <v>335802000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>221215000</v>
+        <v>73510000</v>
       </c>
       <c r="AK2" t="n">
-        <v>218559000</v>
+        <v>66826000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2656000</v>
+        <v>6684000</v>
       </c>
       <c r="AM2" t="n">
-        <v>2322749000</v>
+        <v>1374083000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1648426000</v>
+        <v>674657000</v>
       </c>
       <c r="AO2" t="n">
-        <v>35855000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>68776000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>155000000</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>8440000</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>1091000</v>
+        <v>927000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1091000</v>
+        <v>927000</v>
       </c>
       <c r="AT2" t="n">
-        <v>580335000</v>
+        <v>163060000</v>
       </c>
       <c r="AU2" t="n">
-        <v>499320000</v>
+        <v>108690000</v>
       </c>
       <c r="AV2" t="n">
-        <v>81015000</v>
+        <v>54370000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1022705000</v>
+        <v>286894000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-175958000</v>
+        <v>-115990000</v>
       </c>
       <c r="AY2" t="n">
-        <v>1198663000</v>
+        <v>402884000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>25254000</v>
+        <v>4037000</v>
       </c>
       <c r="BA2" t="n">
-        <v>108637000</v>
+        <v>54719000</v>
       </c>
       <c r="BB2" t="n">
-        <v>28797000</v>
+        <v>22312000</v>
       </c>
       <c r="BC2" t="n">
-        <v>1035975000</v>
+        <v>321816000</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>674323000</v>
+        <v>699426000</v>
       </c>
       <c r="BF2" t="n">
-        <v>84566000</v>
+        <v>35015000</v>
       </c>
       <c r="BG2" t="n">
-        <v>10572000</v>
+        <v>4125000</v>
       </c>
       <c r="BH2" t="n">
-        <v>176000000</v>
+        <v>187000000</v>
       </c>
       <c r="BI2" t="n">
-        <v>24896000</v>
+        <v>16033000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>38030000</v>
+        <v>65405000</v>
       </c>
       <c r="BK2" t="n">
-        <v>22099000</v>
+        <v>10997000</v>
       </c>
       <c r="BL2" t="n">
-        <v>-913000</v>
+        <v>-1409000</v>
       </c>
       <c r="BM2" t="n">
-        <v>23012000</v>
+        <v>12406000</v>
       </c>
       <c r="BN2" t="n">
-        <v>318160000</v>
+        <v>396884000</v>
       </c>
       <c r="BO2" t="n">
-        <v>47906000</v>
+        <v>62552000</v>
       </c>
       <c r="BP2" t="n">
-        <v>270254000</v>
+        <v>334332000</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>270254000</v>
+        <v>334332000</v>
       </c>
     </row>
     <row r="3">
@@ -1847,212 +1851,208 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1167216000</v>
+        <v>1161204000</v>
       </c>
       <c r="C4" t="n">
-        <v>1167216000</v>
+        <v>1161204000</v>
       </c>
       <c r="D4" t="n">
-        <v>112136000</v>
+        <v>605407000</v>
       </c>
       <c r="E4" t="n">
-        <v>483417000</v>
+        <v>951860000</v>
       </c>
       <c r="F4" t="n">
-        <v>514782000</v>
+        <v>198025000</v>
       </c>
       <c r="G4" t="n">
-        <v>1124310000</v>
+        <v>1654021000</v>
       </c>
       <c r="H4" t="n">
-        <v>146172000</v>
+        <v>-315233000</v>
       </c>
       <c r="I4" t="n">
-        <v>514782000</v>
+        <v>198025000</v>
       </c>
       <c r="J4" t="n">
-        <v>36949000</v>
+        <v>76199000</v>
       </c>
       <c r="K4" t="n">
-        <v>677842000</v>
+        <v>778360000</v>
       </c>
       <c r="L4" t="n">
-        <v>788508000</v>
+        <v>1082921000</v>
       </c>
       <c r="M4" t="n">
-        <v>685787000</v>
+        <v>781185000</v>
       </c>
       <c r="N4" t="n">
-        <v>7945000</v>
+        <v>2825000</v>
       </c>
       <c r="O4" t="n">
-        <v>677842000</v>
+        <v>778360000</v>
       </c>
       <c r="P4" t="n">
-        <v>5844000</v>
+        <v>2623000</v>
       </c>
       <c r="Q4" t="n">
-        <v>176000</v>
+        <v>168000</v>
       </c>
       <c r="R4" t="n">
-        <v>217067000</v>
+        <v>241942000</v>
       </c>
       <c r="S4" t="n">
-        <v>237765000</v>
+        <v>228298000</v>
       </c>
       <c r="T4" t="n">
-        <v>9801000</v>
+        <v>9750000</v>
       </c>
       <c r="U4" t="n">
-        <v>9801000</v>
+        <v>9750000</v>
       </c>
       <c r="V4" t="n">
-        <v>688296000</v>
+        <v>1541564000</v>
       </c>
       <c r="W4" t="n">
-        <v>135042000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2978000</v>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+        <v>552008000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>7894000</v>
+      </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>165097000</v>
       </c>
       <c r="AA4" t="n">
-        <v>741000</v>
+        <v>5924000</v>
       </c>
       <c r="AB4" t="n">
-        <v>131323000</v>
+        <v>373093000</v>
       </c>
       <c r="AC4" t="n">
-        <v>20657000</v>
+        <v>68532000</v>
       </c>
       <c r="AD4" t="n">
-        <v>110666000</v>
+        <v>304561000</v>
       </c>
       <c r="AE4" t="n">
-        <v>553254000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>863000</v>
-      </c>
+        <v>989556000</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>352094000</v>
+        <v>578767000</v>
       </c>
       <c r="AH4" t="n">
-        <v>16292000</v>
+        <v>7667000</v>
       </c>
       <c r="AI4" t="n">
-        <v>335802000</v>
+        <v>571100000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>73510000</v>
+        <v>221215000</v>
       </c>
       <c r="AK4" t="n">
-        <v>66826000</v>
+        <v>218559000</v>
       </c>
       <c r="AL4" t="n">
-        <v>6684000</v>
+        <v>2656000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1374083000</v>
+        <v>2322749000</v>
       </c>
       <c r="AN4" t="n">
-        <v>674657000</v>
+        <v>1648426000</v>
       </c>
       <c r="AO4" t="n">
-        <v>68776000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>155000000</v>
-      </c>
+        <v>35855000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>8440000</v>
       </c>
       <c r="AR4" t="n">
-        <v>927000</v>
+        <v>1091000</v>
       </c>
       <c r="AS4" t="n">
-        <v>927000</v>
+        <v>1091000</v>
       </c>
       <c r="AT4" t="n">
-        <v>163060000</v>
+        <v>580335000</v>
       </c>
       <c r="AU4" t="n">
-        <v>108690000</v>
+        <v>499320000</v>
       </c>
       <c r="AV4" t="n">
-        <v>54370000</v>
+        <v>81015000</v>
       </c>
       <c r="AW4" t="n">
-        <v>286894000</v>
+        <v>1022705000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-115990000</v>
+        <v>-175958000</v>
       </c>
       <c r="AY4" t="n">
-        <v>402884000</v>
+        <v>1198663000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4037000</v>
+        <v>25254000</v>
       </c>
       <c r="BA4" t="n">
-        <v>54719000</v>
+        <v>108637000</v>
       </c>
       <c r="BB4" t="n">
-        <v>22312000</v>
+        <v>28797000</v>
       </c>
       <c r="BC4" t="n">
-        <v>321816000</v>
+        <v>1035975000</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>699426000</v>
+        <v>674323000</v>
       </c>
       <c r="BF4" t="n">
-        <v>35015000</v>
+        <v>84566000</v>
       </c>
       <c r="BG4" t="n">
-        <v>4125000</v>
+        <v>10572000</v>
       </c>
       <c r="BH4" t="n">
-        <v>187000000</v>
+        <v>176000000</v>
       </c>
       <c r="BI4" t="n">
-        <v>16033000</v>
+        <v>24896000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>65405000</v>
+        <v>38030000</v>
       </c>
       <c r="BK4" t="n">
-        <v>10997000</v>
+        <v>22099000</v>
       </c>
       <c r="BL4" t="n">
-        <v>-1409000</v>
+        <v>-913000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12406000</v>
+        <v>23012000</v>
       </c>
       <c r="BN4" t="n">
-        <v>396884000</v>
+        <v>318160000</v>
       </c>
       <c r="BO4" t="n">
-        <v>62552000</v>
+        <v>47906000</v>
       </c>
       <c r="BP4" t="n">
-        <v>334332000</v>
+        <v>270254000</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>334332000</v>
+        <v>270254000</v>
       </c>
     </row>
   </sheetData>
@@ -2338,160 +2338,164 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-87252000</v>
+        <v>-168259000</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-267742000</v>
+        <v>-181252000</v>
       </c>
       <c r="E2" t="n">
-        <v>450020000</v>
+        <v>413759000</v>
       </c>
       <c r="F2" t="n">
-        <v>22000</v>
+        <v>1508000</v>
       </c>
       <c r="G2" t="n">
-        <v>-285091000</v>
+        <v>-259168000</v>
       </c>
       <c r="H2" t="n">
-        <v>270254000</v>
+        <v>334332000</v>
       </c>
       <c r="I2" t="n">
-        <v>212583000</v>
+        <v>357700000</v>
       </c>
       <c r="J2" t="n">
-        <v>4076000</v>
+        <v>-6268000</v>
       </c>
       <c r="K2" t="n">
-        <v>53595000</v>
+        <v>-17100000</v>
       </c>
       <c r="L2" t="n">
-        <v>91779000</v>
+        <v>176592000</v>
       </c>
       <c r="M2" t="n">
-        <v>7000000</v>
+        <v>492000</v>
       </c>
       <c r="N2" t="n">
-        <v>-45684000</v>
+        <v>-26634000</v>
       </c>
       <c r="O2" t="n">
-        <v>-8545000</v>
+        <v>-14545000</v>
       </c>
       <c r="P2" t="n">
-        <v>22000</v>
+        <v>1508000</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>22000</v>
+        <v>1508000</v>
       </c>
       <c r="S2" t="n">
-        <v>182278000</v>
+        <v>232507000</v>
       </c>
       <c r="T2" t="n">
-        <v>182278000</v>
+        <v>232507000</v>
       </c>
       <c r="U2" t="n">
-        <v>-267742000</v>
+        <v>-181252000</v>
       </c>
       <c r="V2" t="n">
-        <v>450020000</v>
+        <v>413759000</v>
       </c>
       <c r="W2" t="n">
-        <v>-236023000</v>
+        <v>-284601000</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>1212000</v>
+        <v>3292000</v>
       </c>
       <c r="Z2" t="n">
-        <v>51436000</v>
+        <v>3922000</v>
       </c>
       <c r="AA2" t="n">
-        <v>52942000</v>
+        <v>3922000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1506000</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3580000</v>
+        <v>-11583000</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-3580000</v>
+        <v>-11583000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-3339000</v>
+        <v>-4073000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3339000</v>
+        <v>-4073000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-281752000</v>
+        <v>-254579000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>516000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-281752000</v>
+        <v>-255095000</v>
       </c>
       <c r="AK2" t="n">
-        <v>197839000</v>
+        <v>90909000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-216000</v>
+        <v>-1211000</v>
       </c>
       <c r="AM2" t="n">
-        <v>4788000</v>
+        <v>4053000</v>
       </c>
       <c r="AN2" t="n">
-        <v>38031000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>-18984000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>267000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>30666000</v>
+        <v>-8134000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>20087000</v>
+        <v>2511000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-15325000</v>
+        <v>-2805000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2603000</v>
+        <v>-10556000</v>
       </c>
       <c r="AT2" t="n">
-        <v>22922000</v>
+        <v>3224000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1854000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>6784000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-621000</v>
+      </c>
       <c r="AW2" t="n">
-        <v>85882000</v>
+        <v>47526000</v>
       </c>
       <c r="AX2" t="n">
-        <v>8026000</v>
+        <v>2634000</v>
       </c>
       <c r="AY2" t="n">
-        <v>77856000</v>
+        <v>44892000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-3862000</v>
+        <v>3767000</v>
       </c>
       <c r="BA2" t="n">
-        <v>871000</v>
+        <v>1169000</v>
       </c>
       <c r="BB2" t="n">
-        <v>39160000</v>
+        <v>28394000</v>
       </c>
     </row>
     <row r="3">
@@ -2656,164 +2660,160 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-168259000</v>
+        <v>-87252000</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-181252000</v>
+        <v>-267742000</v>
       </c>
       <c r="E4" t="n">
-        <v>413759000</v>
+        <v>450020000</v>
       </c>
       <c r="F4" t="n">
-        <v>1508000</v>
+        <v>22000</v>
       </c>
       <c r="G4" t="n">
-        <v>-259168000</v>
+        <v>-285091000</v>
       </c>
       <c r="H4" t="n">
-        <v>334332000</v>
+        <v>270254000</v>
       </c>
       <c r="I4" t="n">
-        <v>357700000</v>
+        <v>212583000</v>
       </c>
       <c r="J4" t="n">
-        <v>-6268000</v>
+        <v>4076000</v>
       </c>
       <c r="K4" t="n">
-        <v>-17100000</v>
+        <v>53595000</v>
       </c>
       <c r="L4" t="n">
-        <v>176592000</v>
+        <v>91779000</v>
       </c>
       <c r="M4" t="n">
-        <v>492000</v>
+        <v>7000000</v>
       </c>
       <c r="N4" t="n">
-        <v>-26634000</v>
+        <v>-45684000</v>
       </c>
       <c r="O4" t="n">
-        <v>-14545000</v>
+        <v>-8545000</v>
       </c>
       <c r="P4" t="n">
-        <v>1508000</v>
+        <v>22000</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1508000</v>
+        <v>22000</v>
       </c>
       <c r="S4" t="n">
-        <v>232507000</v>
+        <v>182278000</v>
       </c>
       <c r="T4" t="n">
-        <v>232507000</v>
+        <v>182278000</v>
       </c>
       <c r="U4" t="n">
-        <v>-181252000</v>
+        <v>-267742000</v>
       </c>
       <c r="V4" t="n">
-        <v>413759000</v>
+        <v>450020000</v>
       </c>
       <c r="W4" t="n">
-        <v>-284601000</v>
+        <v>-236023000</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>3292000</v>
+        <v>1212000</v>
       </c>
       <c r="Z4" t="n">
-        <v>3922000</v>
+        <v>51436000</v>
       </c>
       <c r="AA4" t="n">
-        <v>3922000</v>
+        <v>52942000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-1506000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-11583000</v>
+        <v>-3580000</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-11583000</v>
+        <v>-3580000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-4073000</v>
+        <v>-3339000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4073000</v>
+        <v>-3339000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-254579000</v>
+        <v>-281752000</v>
       </c>
       <c r="AI4" t="n">
-        <v>516000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-255095000</v>
+        <v>-281752000</v>
       </c>
       <c r="AK4" t="n">
-        <v>90909000</v>
+        <v>197839000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1211000</v>
+        <v>-216000</v>
       </c>
       <c r="AM4" t="n">
-        <v>4053000</v>
+        <v>4788000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-18984000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>267000</v>
-      </c>
+        <v>38031000</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>-8134000</v>
+        <v>30666000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2511000</v>
+        <v>20087000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2805000</v>
+        <v>-15325000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-10556000</v>
+        <v>2603000</v>
       </c>
       <c r="AT4" t="n">
-        <v>3224000</v>
+        <v>22922000</v>
       </c>
       <c r="AU4" t="n">
-        <v>6784000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-621000</v>
-      </c>
+        <v>1854000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>47526000</v>
+        <v>85882000</v>
       </c>
       <c r="AX4" t="n">
-        <v>2634000</v>
+        <v>8026000</v>
       </c>
       <c r="AY4" t="n">
-        <v>44892000</v>
+        <v>77856000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3767000</v>
+        <v>-3862000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1169000</v>
+        <v>871000</v>
       </c>
       <c r="BB4" t="n">
-        <v>28394000</v>
+        <v>39160000</v>
       </c>
     </row>
   </sheetData>
@@ -3363,192 +3363,192 @@
       </c>
       <c r="DC1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EO1" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Ms. Hongwei  Liu', 'age': 42, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1983, 'fiscalYear': 2023, 'totalPay': 283818, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Caiyin  Ren', 'age': 48, 'title': 'Executive Director', 'yearBorn': 1977, 'fiscalYear': 2023, 'totalPay': 237480, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yongsheng  Wang', 'age': 55, 'title': 'Executive VP &amp; CFO', 'yearBorn': 1970, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Lijing  Wang', 'age': 44, 'title': 'Executive Vice President', 'yearBorn': 1981, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Tianhang  Liu', 'age': 45, 'title': 'Executive Vice President', 'yearBorn': 1980, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xingli  Li', 'age': 51, 'title': 'VP &amp; President of the College and Supply Chain Segment', 'yearBorn': 1974, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hua  Li', 'age': 45, 'title': 'Executive Director', 'yearBorn': 1980, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Huan  Wu', 'age': 42, 'title': 'Executive Director', 'yearBorn': 1983, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chi Kit  Leung', 'age': 44, 'title': 'Company Secretary', 'yearBorn': 1981, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Ms. Hongwei  Liu', 'age': 42, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1983, 'fiscalYear': 2023, 'totalPay': 283592, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Caiyin  Ren', 'age': 48, 'title': 'Executive Director', 'yearBorn': 1977, 'fiscalYear': 2023, 'totalPay': 237291, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yongsheng  Wang', 'age': 55, 'title': 'Executive VP &amp; CFO', 'yearBorn': 1970, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Lijing  Wang', 'age': 44, 'title': 'Executive Vice President', 'yearBorn': 1981, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Tianhang  Liu', 'age': 45, 'title': 'Executive Vice President', 'yearBorn': 1980, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xingli  Li', 'age': 51, 'title': 'VP &amp; President of the College and Supply Chain Segment', 'yearBorn': 1974, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hua  Li', 'age': 45, 'title': 'Executive Director', 'yearBorn': 1980, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Huan  Wu', 'age': 42, 'title': 'Executive Director', 'yearBorn': 1983, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chi Kit  Leung', 'age': 44, 'title': 'Company Secretary', 'yearBorn': 1981, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3676,7 +3676,7 @@
         <v>0.2232</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.337</v>
+        <v>-0.318</v>
       </c>
       <c r="AE2" t="n">
         <v>2.775</v>
@@ -3774,10 +3774,10 @@
         <v>1161204000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.8257551</v>
+        <v>0.82583857</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.13442242</v>
+        <v>0.13440883</v>
       </c>
       <c r="BL2" t="n">
         <v>1703980800</v>
@@ -3810,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="n">
         <v>0.008</v>
@@ -3928,141 +3928,141 @@
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DD2" t="n">
+          <t>21CENTURY EDU</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>China 21st Century Education Group Limited</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
         <v>-0.892859</v>
       </c>
-      <c r="DE2" t="n">
+      <c r="DF2" t="n">
         <v>0.111</v>
       </c>
-      <c r="DF2" t="b">
-        <v>0</v>
-      </c>
       <c r="DG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>finmb_564870579</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>1742261614</v>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
         <v>1527557400000</v>
       </c>
-      <c r="DH2" t="n">
+      <c r="DV2" t="n">
         <v>-0.001000002</v>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>0.11 - 0.111</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="n">
+      <c r="DY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
         <v>0.001000002</v>
       </c>
-      <c r="DM2" t="n">
+      <c r="EA2" t="n">
         <v>0.009090927</v>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>0.11 - 0.111</t>
         </is>
       </c>
-      <c r="DO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
+      <c r="EC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
         <v>1742986740</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="EG2" t="n">
         <v>1743422400</v>
       </c>
-      <c r="DT2" t="b">
+      <c r="EH2" t="b">
         <v>1</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="EI2" t="n">
         <v>0.04</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="EJ2" t="n">
         <v>0.06</v>
       </c>
-      <c r="DW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>1742261614</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>finmb_564870579</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>21CENTURY EDU</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>China 21st Century Education Group Limited</t>
-        </is>
+      <c r="EK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>0</v>
       </c>
       <c r="EO2" t="inlineStr"/>
     </row>
